--- a/Result/profitability/6228.xlsx
+++ b/Result/profitability/6228.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.12125</v>
+        <v>-0.11625</v>
       </c>
       <c r="N2" t="n">
-        <v>41.80875</v>
+        <v>42.93625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0425</v>
+        <v>-0.04375000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>44.69875</v>
+        <v>47.73</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01875</v>
+        <v>-0.04250000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>48.87375</v>
+        <v>47.6125</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0475</v>
+        <v>0.006249999999999992</v>
       </c>
       <c r="N5" t="n">
-        <v>49.57375</v>
+        <v>49.755</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06125</v>
+        <v>0.03499999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>51.80875</v>
+        <v>50.05875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05875</v>
+        <v>0.002499999999999992</v>
       </c>
       <c r="N7" t="n">
-        <v>52.215</v>
+        <v>45.12625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.002499999999999999</v>
+        <v>-0.02125000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>43.67375</v>
+        <v>42.96749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0475</v>
+        <v>0.04749999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>42.69875</v>
@@ -1645,7 +1645,7 @@
         <v>0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05625000000000001</v>
+        <v>0.05624999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>43.3425</v>
@@ -1772,7 +1772,7 @@
         <v>0.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01500000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="N11" t="n">
         <v>43.4675</v>
@@ -1899,7 +1899,7 @@
         <v>0.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="N12" t="n">
         <v>42.65</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-59.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.80625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.649999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1449089510130802</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6615384615384616</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.450000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04546879899655076</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
